--- a/Playwright_Whatsapp_bot/whatsapp_report_2026-06-18.xlsx
+++ b/Playwright_Whatsapp_bot/whatsapp_report_2026-06-18.xlsx
@@ -477,7 +477,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>c:\Users\vikyd\Downloads\GenAi Program\Playwright_Whatsapp_bot\screenshots\Vikram_2026-06-18.png</t>
+          <t>C:\Users\vikyd\Downloads\GenAi Program\Playwright_Whatsapp_bot\screenshots\Vikram_2026-06-18.png</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
